--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92553181588</v>
+        <v>46157.9310626445</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9310626445</v>
+        <v>46157.93131965079</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93131965079</v>
+        <v>46157.93380020159</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93380020159</v>
+        <v>46157.93690414434</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93690414434</v>
+        <v>46158.28203053738</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28203053738</v>
+        <v>46158.29734047251</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29734047251</v>
+        <v>46158.29803126045</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29803126045</v>
+        <v>46158.3336688738</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3336688738</v>
+        <v>46158.37218685287</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37218685287</v>
+        <v>46158.37273629029</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
